--- a/Jung_etal_2022/Jung_etal_2022_TableS1_snapshot.xlsx
+++ b/Jung_etal_2022/Jung_etal_2022_TableS1_snapshot.xlsx
@@ -1,67 +1,307 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo-M1-Trait-Data/Jung_etal_2022/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_857420BF19997A656C974F3E229420A93D025A80" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="32940" windowHeight="11600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TableS1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="TableS1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TableS1'!$A$3:$N$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TableS1!$A$3:$N$14</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="73">
+  <si>
+    <t>Jung et al. (2022), Supplementary Table S1</t>
+  </si>
+  <si>
+    <t>Frozen transcription from Table S1. Source: https://www.science.org/doi/suppl/10.1126/sciadv.abn0954/suppl_file/sciadv.abn0954_sm.pdf</t>
+  </si>
+  <si>
+    <t>Species as published</t>
+  </si>
+  <si>
+    <t>Species scientific name</t>
+  </si>
+  <si>
+    <t>V1 size (mm^2)</t>
+  </si>
+  <si>
+    <t>V1 size reference(s)</t>
+  </si>
+  <si>
+    <t>Retina size (mm^2)</t>
+  </si>
+  <si>
+    <t>Retina size reference(s)</t>
+  </si>
+  <si>
+    <t>Size ratio (V1/Retina)</t>
+  </si>
+  <si>
+    <t>2D number of V1 neurons (x10^3)</t>
+  </si>
+  <si>
+    <t>V1 neuron reference(s)</t>
+  </si>
+  <si>
+    <t>Number of RGC (x10^3)</t>
+  </si>
+  <si>
+    <t>RGC reference(s)</t>
+  </si>
+  <si>
+    <t>Cell number ratio (V1/RGC)</t>
+  </si>
+  <si>
+    <t>Centroperipheral density (CP ratio)</t>
+  </si>
+  <si>
+    <t>CP ratio reference(s)</t>
+  </si>
+  <si>
+    <t>Mouse</t>
+  </si>
+  <si>
+    <t>Mus musculus</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>79</t>
+  </si>
+  <si>
+    <t>46, 17</t>
+  </si>
+  <si>
+    <t>Rat</t>
+  </si>
+  <si>
+    <t>Rattus norvegicus</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>71, 17</t>
+  </si>
+  <si>
+    <t>Rabbit</t>
+  </si>
+  <si>
+    <t>Oryctolagus cuniculus</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>42, 17</t>
+  </si>
+  <si>
+    <t>Squirrel</t>
+  </si>
+  <si>
+    <t>not specified</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>83, 17</t>
+  </si>
+  <si>
+    <t>Ferret</t>
+  </si>
+  <si>
+    <t>Mustela putorius furo</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>72, 17</t>
+  </si>
+  <si>
+    <t>Tree shrew</t>
+  </si>
+  <si>
+    <t>20, 68</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>84, 17</t>
+  </si>
+  <si>
+    <t>Cat</t>
+  </si>
+  <si>
+    <t>Felis catus</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>74, 17</t>
+  </si>
+  <si>
+    <t>Wallaby</t>
+  </si>
+  <si>
+    <t>Macropus eugenii</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>75, 7</t>
+  </si>
+  <si>
+    <t>Macaque</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>63, 17</t>
+  </si>
+  <si>
+    <t>Agouti</t>
+  </si>
+  <si>
+    <t>Dasyprocta leporina</t>
+  </si>
+  <si>
+    <t>19, 13</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>77, 17</t>
+  </si>
+  <si>
+    <t>Mouse lemur</t>
+  </si>
+  <si>
+    <t>Microcebus murinus</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>78, 17</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.##"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <b/>
       <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="00666666"/>
+      <i/>
       <sz val="9"/>
+      <color rgb="FF666666"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <color rgb="00008000"/>
+      <sz val="11"/>
+      <color rgb="FF008000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="FF1F4E78"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="005B9BD5"/>
+        <fgColor rgb="FF5B9BD5"/>
       </patternFill>
     </fill>
   </fills>
@@ -77,99 +317,41 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -457,734 +639,573 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="26" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="5" width="18" customWidth="1"/>
+    <col min="6" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="24" customWidth="1"/>
+    <col min="9" max="10" width="20" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
+    <col min="12" max="12" width="22" customWidth="1"/>
+    <col min="13" max="13" width="26" customWidth="1"/>
+    <col min="14" max="14" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Jung et al. (2022), Supplementary Table S1</t>
-        </is>
-      </c>
+    <row r="1" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
     </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Frozen transcription from Table S1. Source: https://www.science.org/doi/suppl/10.1126/sciadv.abn0954/suppl_file/sciadv.abn0954_sm.pdf</t>
-        </is>
-      </c>
+    <row r="2" spans="1:14" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
     </row>
-    <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Species as published</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Species scientific name</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>V1 size (mm^2)</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>V1 size reference(s)</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Retina size (mm^2)</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Retina size reference(s)</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>Size ratio (V1/Retina)</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>2D number of V1 neurons (x10^3)</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>V1 neuron reference(s)</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>Number of RGC (x10^3)</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>RGC reference(s)</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>Cell number ratio (V1/RGC)</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>Centroperipheral density (CP ratio)</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>CP ratio reference(s)</t>
-        </is>
+    <row r="3" spans="1:14" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Mouse</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Mus musculus</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n">
+    <row r="4" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="3">
         <v>3</v>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="n">
+      <c r="D4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="3">
         <v>15</v>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="n">
+      <c r="F4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="4">
         <v>0.2</v>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="H4" s="3">
         <v>7</v>
       </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J4" s="5" t="n">
+      <c r="I4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="3">
         <v>70</v>
       </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="n">
+      <c r="K4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" s="4">
         <v>0.09</v>
       </c>
-      <c r="M4" s="5" t="n">
+      <c r="M4" s="3">
         <v>2.7</v>
       </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>46, 17</t>
-        </is>
+      <c r="N4" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Rat</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Rattus norvegicus</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n">
+    <row r="5" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="3">
         <v>7</v>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="n">
+      <c r="D5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="3">
         <v>52</v>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="n">
+      <c r="F5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="4">
         <v>0.13</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="H5" s="3">
         <v>14</v>
       </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="n">
+      <c r="I5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="3">
         <v>110</v>
       </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="L5" s="6" t="n">
+      <c r="K5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" s="4">
         <v>0.13</v>
       </c>
-      <c r="M5" s="5" t="n">
+      <c r="M5" s="3">
         <v>1.4</v>
       </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>71, 17</t>
-        </is>
+      <c r="N5" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Rabbit</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Oryctolagus cuniculus</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n">
+    <row r="6" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="3">
         <v>80</v>
       </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="n">
+      <c r="D6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="3">
         <v>436</v>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="n">
+      <c r="F6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="4">
         <v>0.18</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="H6" s="3">
         <v>162</v>
       </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="n">
+      <c r="I6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="3">
         <v>550</v>
       </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="L6" s="6" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="M6" s="5" t="n">
+      <c r="K6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" s="4">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="M6" s="3">
         <v>2.7</v>
       </c>
-      <c r="N6" s="4" t="inlineStr">
-        <is>
-          <t>42, 17</t>
-        </is>
+      <c r="N6" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Squirrel</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>not specified</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
+    <row r="7" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="3">
         <v>82</v>
       </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="n">
+      <c r="D7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="3">
         <v>205</v>
       </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="n">
+      <c r="F7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="4">
         <v>0.4</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="H7" s="3">
         <v>166</v>
       </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="n">
+      <c r="I7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" s="3">
         <v>1200</v>
       </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="L7" s="6" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="M7" s="5" t="n">
+      <c r="K7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L7" s="4">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="M7" s="3">
         <v>3.2</v>
       </c>
-      <c r="N7" s="4" t="inlineStr">
-        <is>
-          <t>83, 17</t>
-        </is>
+      <c r="N7" s="2" t="s">
+        <v>38</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Ferret</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Mustela putorius furo</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="n">
+    <row r="8" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="3">
         <v>83</v>
       </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="n">
+      <c r="D8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="3">
         <v>84</v>
       </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="n">
+      <c r="F8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="4">
         <v>0.98</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="H8" s="3">
         <v>169</v>
       </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="n">
+      <c r="I8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J8" s="3">
         <v>90</v>
       </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="L8" s="6" t="n">
+      <c r="K8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L8" s="4">
         <v>1.87</v>
       </c>
-      <c r="M8" s="5" t="n">
+      <c r="M8" s="3">
         <v>11</v>
       </c>
-      <c r="N8" s="4" t="inlineStr">
-        <is>
-          <t>72, 17</t>
-        </is>
+      <c r="N8" s="2" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Tree shrew</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>not specified</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="n">
+    <row r="9" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="3">
         <v>83</v>
       </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>20, 68</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="n">
+      <c r="D9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" s="3">
         <v>122</v>
       </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="n">
+      <c r="F9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" s="4">
         <v>0.6</v>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="H9" s="3">
         <v>149</v>
       </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="n">
+      <c r="I9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J9" s="3">
         <v>305</v>
       </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="L9" s="6" t="n">
+      <c r="K9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="L9" s="4">
         <v>0.49</v>
       </c>
-      <c r="M9" s="5" t="n">
+      <c r="M9" s="3">
         <v>7.6</v>
       </c>
-      <c r="N9" s="4" t="inlineStr">
-        <is>
-          <t>84, 17</t>
-        </is>
+      <c r="N9" s="2" t="s">
+        <v>48</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Cat</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Felis catus</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n">
+    <row r="10" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="3">
         <v>380</v>
       </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="n">
+      <c r="D10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="3">
         <v>510</v>
       </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="n">
+      <c r="F10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10" s="4">
         <v>0.75</v>
       </c>
-      <c r="H10" s="5" t="n">
+      <c r="H10" s="3">
         <v>681</v>
       </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="n">
+      <c r="I10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J10" s="3">
         <v>247</v>
       </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="L10" s="6" t="n">
+      <c r="K10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="L10" s="4">
         <v>2.76</v>
       </c>
-      <c r="M10" s="5" t="n">
+      <c r="M10" s="3">
         <v>36.4</v>
       </c>
-      <c r="N10" s="4" t="inlineStr">
-        <is>
-          <t>74, 17</t>
-        </is>
+      <c r="N10" s="2" t="s">
+        <v>53</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Wallaby</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Macropus eugenii</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="n">
+    <row r="11" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="3">
         <v>135</v>
       </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="n">
+      <c r="D11" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E11" s="3">
         <v>432</v>
       </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="n">
+      <c r="F11" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" s="4">
         <v>0.32</v>
       </c>
-      <c r="H11" s="5" t="n">
+      <c r="H11" s="3">
         <v>273</v>
       </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="n">
+      <c r="I11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J11" s="3">
         <v>360</v>
       </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="L11" s="6" t="n">
+      <c r="K11" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="L11" s="4">
         <v>0.76</v>
       </c>
-      <c r="M11" s="5" t="n">
+      <c r="M11" s="3">
         <v>20</v>
       </c>
-      <c r="N11" s="4" t="inlineStr">
-        <is>
-          <t>75, 7</t>
-        </is>
+      <c r="N11" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Macaque</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>not specified</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="n">
+    <row r="12" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="3">
         <v>1257</v>
       </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="n">
+      <c r="D12" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" s="3">
         <v>636</v>
       </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="n">
+      <c r="F12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G12" s="4">
         <v>1.98</v>
       </c>
-      <c r="H12" s="5" t="n">
+      <c r="H12" s="3">
         <v>3812</v>
       </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="n">
+      <c r="I12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J12" s="3">
         <v>1600</v>
       </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="L12" s="6" t="n">
+      <c r="K12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12" s="4">
         <v>2.38</v>
       </c>
-      <c r="M12" s="5" t="n">
+      <c r="M12" s="3">
         <v>60</v>
       </c>
-      <c r="N12" s="4" t="inlineStr">
-        <is>
-          <t>63, 17</t>
-        </is>
+      <c r="N12" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Agouti</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Dasyprocta leporina</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="n">
+    <row r="13" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="3">
         <v>320</v>
       </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>19, 13</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="n">
+      <c r="D13" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" s="3">
         <v>536</v>
       </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="n">
+      <c r="F13" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G13" s="4">
         <v>0.6</v>
       </c>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="4" t="n"/>
-      <c r="J13" s="5" t="n">
+      <c r="H13" s="3"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="3">
         <v>482</v>
       </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="L13" s="6" t="n"/>
-      <c r="M13" s="5" t="n">
+      <c r="K13" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="L13" s="4"/>
+      <c r="M13" s="3">
         <v>2.9</v>
       </c>
-      <c r="N13" s="4" t="inlineStr">
-        <is>
-          <t>77, 17</t>
-        </is>
+      <c r="N13" s="2" t="s">
+        <v>67</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Mouse lemur</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Microcebus murinus</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="n">
+    <row r="14" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="3">
         <v>48</v>
       </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="n">
+      <c r="D14" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E14" s="3">
         <v>130</v>
       </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="n">
+      <c r="F14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G14" s="4">
         <v>0.36</v>
       </c>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="4" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="4" t="n"/>
-      <c r="L14" s="6" t="n"/>
-      <c r="M14" s="5" t="n">
+      <c r="H14" s="3"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="3">
         <v>22</v>
       </c>
-      <c r="N14" s="4" t="inlineStr">
-        <is>
-          <t>78, 17</t>
-        </is>
+      <c r="N14" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N14"/>
+  <autoFilter ref="A3:N14" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
@@ -1194,6 +1215,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
@@ -1448,34 +1489,46 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CA4496E-F9E9-4676-8BDC-E53ED0030764}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70946532-BB4D-4288-B2D5-26EF2ACC00CD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66533DBD-4CC7-44EC-A129-613DB8E11733}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66533DBD-4CC7-44EC-A129-613DB8E11733}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70946532-BB4D-4288-B2D5-26EF2ACC00CD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CA4496E-F9E9-4676-8BDC-E53ED0030764}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>